--- a/zDocuments/Dashboard structure.xlsx
+++ b/zDocuments/Dashboard structure.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\Sem 5\f1-ml-project\zDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Kapil Pandya\Germany\Philip_Marburg\Project\f1-race-prediction\zDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_AACE1C3105A1736AF9871FA2F38B95AA177E1731" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19368" windowHeight="9192"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -622,7 +623,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -959,23 +960,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="17.77734375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +1005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1036,7 +1037,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -1068,7 +1069,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>27</v>
       </c>
@@ -1100,7 +1101,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
@@ -1132,7 +1133,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>43</v>
       </c>
